--- a/samples/files/Client-and-Lead-Tracker.xlsx
+++ b/samples/files/Client-and-Lead-Tracker.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Client and Lead Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Alder &amp; Finch Co. sales pipeline (fictional sample data)</t>
+    <t xml:space="preserve">Quillbrook Supply Co. sales pipeline (fictional sample data)</t>
   </si>
   <si>
     <t xml:space="preserve">Data as of</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">Overdue</t>
   </si>
   <si>
-    <t xml:space="preserve">Ivy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jen</t>
+    <t xml:space="preserve">Ashley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarah</t>
   </si>
   <si>
     <t xml:space="preserve">Leads</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">L-101</t>
   </si>
   <si>
-    <t xml:space="preserve">Kestrel Hardware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramon Lim</t>
+    <t xml:space="preserve">Pinewick Hardware Supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethan Walker</t>
   </si>
   <si>
     <t xml:space="preserve">Referral</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">L-102</t>
   </si>
   <si>
-    <t xml:space="preserve">Brightwell Logistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Chua</t>
+    <t xml:space="preserve">Tallowmere Freight Co.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Megan Brooks</t>
   </si>
   <si>
     <t xml:space="preserve">LinkedIn</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">L-103</t>
   </si>
   <si>
-    <t xml:space="preserve">Bayside Packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leo Santos</t>
+    <t xml:space="preserve">Cobbleton Packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Hayes</t>
   </si>
   <si>
     <t xml:space="preserve">Trade show</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">L-104</t>
   </si>
   <si>
-    <t xml:space="preserve">Silverleaf Hotels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grace Tan</t>
+    <t xml:space="preserve">Marrowind Inn Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauren Mitchell</t>
   </si>
   <si>
     <t xml:space="preserve">Send intro email</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">L-105</t>
   </si>
   <si>
-    <t xml:space="preserve">Marlowe Foods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana Villanueva</t>
+    <t xml:space="preserve">Hollisford Foods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachel Coleman</t>
   </si>
   <si>
     <t xml:space="preserve">Send revised pricing</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">L-106</t>
   </si>
   <si>
-    <t xml:space="preserve">Crestview Schools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liza Aquino</t>
+    <t xml:space="preserve">Fernhollow Academy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Reed</t>
   </si>
   <si>
     <t xml:space="preserve">Website</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">L-107</t>
   </si>
   <si>
-    <t xml:space="preserve">Northgate Pharmacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paolo Reyes</t>
+    <t xml:space="preserve">Ashcombe Family Pharmacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jessica Turner</t>
   </si>
   <si>
     <t xml:space="preserve">Cold email</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">L-108</t>
   </si>
   <si>
-    <t xml:space="preserve">Pinecrest Clinics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joy Mendoza</t>
+    <t xml:space="preserve">Willowmarch Clinics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin Sullivan</t>
   </si>
   <si>
     <t xml:space="preserve">Send case study</t>
@@ -281,10 +281,10 @@
     <t xml:space="preserve">L-109</t>
   </si>
   <si>
-    <t xml:space="preserve">Oakline Furniture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Uy</t>
+    <t xml:space="preserve">Bramblewood Furniture Works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amanda Price</t>
   </si>
   <si>
     <t xml:space="preserve">Legal review of terms</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">L-110</t>
   </si>
   <si>
-    <t xml:space="preserve">Harlow Retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kim Dela Cruz</t>
+    <t xml:space="preserve">Quarrystone Retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Bennett</t>
   </si>
   <si>
     <t xml:space="preserve">Kickoff call</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">L-111</t>
   </si>
   <si>
-    <t xml:space="preserve">Tidewater Grocers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bea Ramos</t>
+    <t xml:space="preserve">Larkhaven Grocers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emily Foster</t>
   </si>
   <si>
     <t xml:space="preserve">Onboarding checklist</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">L-112</t>
   </si>
   <si>
-    <t xml:space="preserve">Ember Cafe Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nico Garcia</t>
+    <t xml:space="preserve">Copperkettle Cafe Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Parker</t>
   </si>
   <si>
     <t xml:space="preserve">Instagram</t>
@@ -429,14 +429,14 @@
     </font>
     <font>
       <sz val="20"/>
-      <color rgb="FF1F2833"/>
+      <color rgb="FF2E3031"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF667181"/>
+      <color rgb="FF6B7075"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -444,14 +444,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF667181"/>
+      <color rgb="FF6B7075"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF2F6399"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -459,7 +459,7 @@
     <font>
       <i val="true"/>
       <sz val="9"/>
-      <color rgb="FF667181"/>
+      <color rgb="FF6B7075"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -467,14 +467,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF0B6FB3"/>
+      <color rgb="FF2F6399"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF1F2833"/>
+      <color rgb="FF2E3031"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -482,7 +482,7 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF1F2833"/>
+      <color rgb="FF2E3031"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -490,7 +490,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1F2833"/>
+      <color rgb="FF2E3031"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -523,8 +523,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1F1FD"/>
-        <bgColor rgb="FFE2E8F0"/>
+        <fgColor rgb="FFDCEAF5"/>
+        <bgColor rgb="FFE3E7EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -541,22 +541,22 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFE3E7EB"/>
       </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFE3E7EB"/>
       </left>
       <right style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFE3E7EB"/>
       </right>
       <top style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFE3E7EB"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFE3E7EB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -586,88 +586,92 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -680,26 +684,26 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="17">
     <dxf>
       <font>
         <name val="Arial"/>
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF94465B"/>
+        <color rgb="FF2E3031"/>
         <sz val="12"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFCF2F4"/>
+          <bgColor rgb="FFE6E7E8"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE1F1FD"/>
+          <fgColor rgb="FFDCEAF5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -714,7 +718,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF0B6FB3"/>
+          <fgColor rgb="FF2E3031"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -722,7 +726,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF1F2833"/>
+          <fgColor rgb="FF2F6399"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -730,7 +734,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
+          <fgColor rgb="FFD4E5F3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -738,7 +742,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEFF6F2"/>
+          <fgColor rgb="FFE6E7E8"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -746,7 +750,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF2F9FF"/>
+          <fgColor rgb="FFEEF5FB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -754,7 +758,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4F3FC"/>
+          <fgColor rgb="FF4F8BC9"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -762,7 +766,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFBF6EC"/>
+          <fgColor rgb="FFF7F7F7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -770,55 +774,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCF2F4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF3D6A55"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF57519A"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF85632A"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94465B"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8FB"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF667181"/>
+          <fgColor rgb="FF6B7075"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -829,12 +785,12 @@
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF94465B"/>
+        <color rgb="FF2E3031"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFCF2F4"/>
+          <bgColor rgb="FFE6E7E8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -844,12 +800,12 @@
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF85632A"/>
+        <color rgb="FF2E3031"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFBF6EC"/>
+          <bgColor rgb="FFD4E5F3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -859,12 +815,12 @@
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF0B6FB3"/>
+        <color rgb="FF2F6399"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF2F9FF"/>
+          <bgColor rgb="FFEEF5FB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -874,12 +830,12 @@
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF667181"/>
+        <color rgb="FF6B7075"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF6F8FB"/>
+          <bgColor rgb="FFF7F7F7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -889,12 +845,12 @@
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF3D6A55"/>
+        <color rgb="FF2F6399"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFEFF6F2"/>
+          <bgColor rgb="FFDCEAF5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -904,12 +860,12 @@
         <charset val="1"/>
         <family val="0"/>
         <b val="1"/>
-        <color rgb="FF57519A"/>
+        <color rgb="FF4F8BC9"/>
         <sz val="10"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF4F3FC"/>
+          <bgColor rgb="FFEEF5FB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -917,7 +873,7 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFF6F8FB"/>
+      <rgbColor rgb="FFF7F7F7"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
@@ -927,19 +883,19 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF85632A"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF0A78C2"/>
-      <rgbColor rgb="FFD2AE6B"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF878787"/>
-      <rgbColor rgb="FFA19DDB"/>
-      <rgbColor rgb="FF94465B"/>
-      <rgbColor rgb="FFFBF6EC"/>
-      <rgbColor rgb="FFE1F1FD"/>
+      <rgbColor rgb="FF70A6D4"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFEEF5FB"/>
+      <rgbColor rgb="FFDCEAF5"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0B6FB3"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF2F6399"/>
+      <rgbColor rgb="FFB9D3E8"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -949,29 +905,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEFF6F2"/>
-      <rgbColor rgb="FFE2E8F0"/>
-      <rgbColor rgb="FFFCF2F4"/>
-      <rgbColor rgb="FFF2F9FF"/>
+      <rgbColor rgb="FFD4E5F3"/>
+      <rgbColor rgb="FFE3E7EB"/>
+      <rgbColor rgb="FFE6E7E8"/>
+      <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF4F3FC"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF5BB5EE"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF4F8BC9"/>
+      <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF667181"/>
-      <rgbColor rgb="FF86B39B"/>
+      <rgbColor rgb="FF6B7075"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF3D6A55"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF57519A"/>
-      <rgbColor rgb="FF1F2833"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF2E3031"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1038,11 +994,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="5bb5ee"/>
+              <a:srgbClr val="70a6d4"/>
             </a:solidFill>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="5bb5ee"/>
+                <a:srgbClr val="70a6d4"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1133,17 +1089,17 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="85629321"/>
-        <c:axId val="82658979"/>
+        <c:axId val="28674807"/>
+        <c:axId val="22308791"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85629321"/>
+        <c:axId val="28674807"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1169,7 +1125,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82658979"/>
+        <c:crossAx val="22308791"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1177,7 +1133,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82658979"/>
+        <c:axId val="22308791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1209,7 +1165,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85629321"/>
+        <c:crossAx val="28674807"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1248,9 +1204,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>507600</xdr:colOff>
+      <xdr:colOff>507240</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>126000</xdr:rowOff>
+      <xdr:rowOff>125640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1259,7 +1215,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="5686560" y="1143000"/>
-        <a:ext cx="5399640" cy="3059640"/>
+        <a:ext cx="5399280" cy="3059280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1470,265 +1426,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF0A78C2"/>
+    <tabColor rgb="FF70A6D4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:E28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>46300</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>1828000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="10" t="n">
         <f aca="false">COUNTIFS(Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,"Won")</f>
         <v>885000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <f aca="false">COUNTIFS(Leads!$L$5:$L$300,"Overdue")+COUNTIFS(Leads!$L$5:$L$300,"Due today")+COUNTIFS(Leads!$L$5:$L$300,"This week")</f>
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <f aca="false">COUNTIFS(Leads!$L$5:$L$300,"Overdue")</f>
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <f aca="false">IFERROR(COUNTIFS(Leads!$F$5:$F$300,"Won")/(COUNTIFS(Leads!$F$5:$F$300,"Won")+COUNTIFS(Leads!$F$5:$F$300,"Lost")),0)</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$F$5:$F$300,B16)</f>
         <v>2</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,B16)</f>
         <v>370000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$F$5:$F$300,B17)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,B17)</f>
         <v>383000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$F$5:$F$300,B18)</f>
         <v>2</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,B18)</f>
         <v>325000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$F$5:$F$300,B19)</f>
         <v>2</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,B19)</f>
         <v>750000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$F$5:$F$300,B20)</f>
         <v>2</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,B20)</f>
         <v>885000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$F$5:$F$300,B21)</f>
         <v>1</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$F$5:$F$300,B21)</f>
         <v>60000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="15" t="n">
         <f aca="false">SUM(C16:C21)</f>
         <v>12</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
         <f aca="false">SUM(D16:D21)</f>
         <v>2773000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C26" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$H$5:$H$300,B26,Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>3</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$H$5:$H$300,B26,Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>790000</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$H$5:$H$300,B26,Leads!$L$5:$L$300,"Overdue")</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$H$5:$H$300,B27,Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>4</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$H$5:$H$300,B27,Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>865000</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$H$5:$H$300,B27,Leads!$L$5:$L$300,"Overdue")</f>
         <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$H$5:$H$300,B28,Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="13" t="n">
         <f aca="false">SUMIFS(Leads!$G$5:$G$300,Leads!$H$5:$H$300,B28,Leads!$F$5:$F$300,"&lt;&gt;Won",Leads!$F$5:$F$300,"&lt;&gt;Lost",Leads!$F$5:$F$300,"&lt;&gt;")</f>
         <v>173000</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <f aca="false">COUNTIFS(Leads!$H$5:$H$300,B28,Leads!$L$5:$L$300,"Overdue")</f>
         <v>0</v>
       </c>
@@ -1754,579 +1710,579 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF86B39B"/>
+    <tabColor rgb="FF4F8BC9"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:M16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>140000</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>46289</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>46297</v>
       </c>
-      <c r="L5" s="13" t="str">
+      <c r="L5" s="14" t="str">
         <f aca="false">IF(F5="","",IF(OR(F5="Won",F5="Lost"),"Closed",IF(K5&lt;Dashboard!$C$4,"Overdue",IF(K5=Dashboard!$C$4,"Due today",IF(K5&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>Overdue</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="12" t="n">
         <f aca="false">IF(OR(K5="",L5="Closed"),"",K5-Dashboard!$C$4)</f>
         <v>-3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>210000</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>46293</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>46298</v>
       </c>
-      <c r="L6" s="13" t="str">
+      <c r="L6" s="14" t="str">
         <f aca="false">IF(F6="","",IF(OR(F6="Won",F6="Lost"),"Closed",IF(K6&lt;Dashboard!$C$4,"Overdue",IF(K6=Dashboard!$C$4,"Due today",IF(K6&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>Overdue</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="12" t="n">
         <f aca="false">IF(OR(K6="",L6="Closed"),"",K6-Dashboard!$C$4)</f>
         <v>-2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <v>185000</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>46294</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="5" t="n">
         <v>46300</v>
       </c>
-      <c r="L7" s="13" t="str">
+      <c r="L7" s="14" t="str">
         <f aca="false">IF(F7="","",IF(OR(F7="Won",F7="Lost"),"Closed",IF(K7&lt;Dashboard!$C$4,"Overdue",IF(K7=Dashboard!$C$4,"Due today",IF(K7&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>Due today</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="12" t="n">
         <f aca="false">IF(OR(K7="",L7="Closed"),"",K7-Dashboard!$C$4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <v>250000</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="16" t="s">
+      <c r="I8" s="5"/>
+      <c r="J8" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="5" t="n">
         <v>46300</v>
       </c>
-      <c r="L8" s="13" t="str">
+      <c r="L8" s="14" t="str">
         <f aca="false">IF(F8="","",IF(OR(F8="Won",F8="Lost"),"Closed",IF(K8&lt;Dashboard!$C$4,"Overdue",IF(K8=Dashboard!$C$4,"Due today",IF(K8&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>Due today</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="12" t="n">
         <f aca="false">IF(OR(K8="",L8="Closed"),"",K8-Dashboard!$C$4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>420000</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>46296</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="5" t="n">
         <v>46301</v>
       </c>
-      <c r="L9" s="13" t="str">
+      <c r="L9" s="14" t="str">
         <f aca="false">IF(F9="","",IF(OR(F9="Won",F9="Lost"),"Closed",IF(K9&lt;Dashboard!$C$4,"Overdue",IF(K9=Dashboard!$C$4,"Due today",IF(K9&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>This week</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="12" t="n">
         <f aca="false">IF(OR(K9="",L9="Closed"),"",K9-Dashboard!$C$4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>120000</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="16" t="s">
+      <c r="I10" s="5"/>
+      <c r="J10" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="5" t="n">
         <v>46301</v>
       </c>
-      <c r="L10" s="13" t="str">
+      <c r="L10" s="14" t="str">
         <f aca="false">IF(F10="","",IF(OR(F10="Won",F10="Lost"),"Closed",IF(K10&lt;Dashboard!$C$4,"Overdue",IF(K10=Dashboard!$C$4,"Due today",IF(K10&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>This week</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="M10" s="12" t="n">
         <f aca="false">IF(OR(K10="",L10="Closed"),"",K10-Dashboard!$C$4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>95000</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>46295</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="K11" s="5" t="n">
         <v>46302</v>
       </c>
-      <c r="L11" s="13" t="str">
+      <c r="L11" s="14" t="str">
         <f aca="false">IF(F11="","",IF(OR(F11="Won",F11="Lost"),"Closed",IF(K11&lt;Dashboard!$C$4,"Overdue",IF(K11=Dashboard!$C$4,"Due today",IF(K11&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>This week</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="12" t="n">
         <f aca="false">IF(OR(K11="",L11="Closed"),"",K11-Dashboard!$C$4)</f>
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>78000</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="5" t="n">
         <v>46297</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="K12" s="5" t="n">
         <v>46303</v>
       </c>
-      <c r="L12" s="13" t="str">
+      <c r="L12" s="14" t="str">
         <f aca="false">IF(F12="","",IF(OR(F12="Won",F12="Lost"),"Closed",IF(K12&lt;Dashboard!$C$4,"Overdue",IF(K12=Dashboard!$C$4,"Due today",IF(K12&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>This week</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="12" t="n">
         <f aca="false">IF(OR(K12="",L12="Closed"),"",K12-Dashboard!$C$4)</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>330000</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="5" t="n">
         <v>46296</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K13" s="5" t="n">
         <v>46304</v>
       </c>
-      <c r="L13" s="13" t="str">
+      <c r="L13" s="14" t="str">
         <f aca="false">IF(F13="","",IF(OR(F13="Won",F13="Lost"),"Closed",IF(K13&lt;Dashboard!$C$4,"Overdue",IF(K13=Dashboard!$C$4,"Due today",IF(K13&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>This week</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="M13" s="12" t="n">
         <f aca="false">IF(OR(K13="",L13="Closed"),"",K13-Dashboard!$C$4)</f>
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>610000</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="5" t="n">
         <v>46290</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K14" s="5" t="n">
         <v>46307</v>
       </c>
-      <c r="L14" s="13" t="str">
+      <c r="L14" s="14" t="str">
         <f aca="false">IF(F14="","",IF(OR(F14="Won",F14="Lost"),"Closed",IF(K14&lt;Dashboard!$C$4,"Overdue",IF(K14=Dashboard!$C$4,"Due today",IF(K14&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>Closed</v>
       </c>
-      <c r="M14" s="11" t="str">
+      <c r="M14" s="12" t="str">
         <f aca="false">IF(OR(K14="",L14="Closed"),"",K14-Dashboard!$C$4)</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>275000</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="5" t="n">
         <v>46283</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="K15" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="L15" s="13" t="str">
+      <c r="L15" s="14" t="str">
         <f aca="false">IF(F15="","",IF(OR(F15="Won",F15="Lost"),"Closed",IF(K15&lt;Dashboard!$C$4,"Overdue",IF(K15=Dashboard!$C$4,"Due today",IF(K15&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>Closed</v>
       </c>
-      <c r="M15" s="11" t="str">
+      <c r="M15" s="12" t="str">
         <f aca="false">IF(OR(K15="",L15="Closed"),"",K15-Dashboard!$C$4)</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>60000</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="5" t="n">
         <v>46280</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="K16" s="5" t="n">
         <v>46399</v>
       </c>
-      <c r="L16" s="13" t="str">
+      <c r="L16" s="14" t="str">
         <f aca="false">IF(F16="","",IF(OR(F16="Won",F16="Lost"),"Closed",IF(K16&lt;Dashboard!$C$4,"Overdue",IF(K16=Dashboard!$C$4,"Due today",IF(K16&lt;=Dashboard!$C$4+6,"This week","Upcoming")))))</f>
         <v>Closed</v>
       </c>
-      <c r="M16" s="11" t="str">
+      <c r="M16" s="12" t="str">
         <f aca="false">IF(OR(K16="",L16="Closed"),"",K16-Dashboard!$C$4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L5:L300">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>"Overdue"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>"Due today"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"This week"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>"Closed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F300">
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>"Won"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>"Lost"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>"Negotiation"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"Proposal"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>"Contacted"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2364,93 +2320,93 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFD2AE6B"/>
+    <tabColor rgb="FFB9D3E8"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2468,91 +2424,91 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFA19DDB"/>
+    <tabColor rgb="FF2F6399"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:C12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="80"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="21" t="s">
         <v>114</v>
       </c>
     </row>
